--- a/program/산출물양식/w2/제출본/[기획] 요구사항 정의서_2차_여행.xlsx
+++ b/program/산출물양식/w2/제출본/[기획] 요구사항 정의서_2차_여행.xlsx
@@ -1164,7 +1164,7 @@
         <is>
           <t>적용: 상태 12종: 신규·분류 중·라우팅 중·실행 중·입력 대기·승인 대기·외부 대기·재개 중·해결·인계·실패·취소.
 인수 REQ-006/AC-01: 고객 신고 또는 감시 변화가 접수되면 출처·대상 여행을 가진 Case가 생성되고 허용된 상태 전이를 따른다.
-인수 REQ-006/AC-02: 같은 스윕·Trip의 여러 사건은 Case 하나로 묶고, 여행·하루 시작 및 출발 안내만으로는 Case를 만들지 않는다.
+인수 REQ-006/AC-02: 같은 감시 회차에서 같은 여행에 발생한 여러 사건은 하나의 처리 건으로 묶는다. 여행·하루 시작 및 출발 안내만으로는 사건 처리 건을 만들지 않는다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -1210,8 +1210,8 @@
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
-          <t>적용: 발기 주체(고객·일정 감시·공급자), 여행 ID 및 사건별 원인·영향 대상. MVP 공급자 이벤트는 Mock이다.
-인수 REQ-007/AC-01: 발생원을 고객·에이전트 요청은 고객, 감시 확인 시점 도래는 일정 도래, 업체 이벤트는 업체로 기록한다.
+          <t>적용: 시작 주체(고객·일정 감시·공급자), 여행 ID 및 사건별 원인·영향 대상. MVP 공급자 이벤트는 Mock이다.
+인수 REQ-007/AC-01: 시작 주체는 고객·에이전트 요청이면 고객, 감시 확인 시점 도래이면 일정 감시, 공급자 이벤트이면 공급자로 기록한다.
 인수 REQ-007/AC-02: 사건을 묶어도 개별 식별자·원인·영향 대상을 조회할 수 있고 Mock 공급자 이벤트는 실제 이벤트와 구별된다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
@@ -1453,14 +1453,14 @@
       </c>
       <c r="E16" s="47" t="inlineStr">
         <is>
-          <t>Registry는 객체 종류와 요청 종류의 두 축으로 Team과 capability를 선택한다.</t>
+          <t>담당 팀 등록부는 객체 종류와 요청 종류를 기준으로 담당 팀을 정한다. 처리 기능은 해당 팀이 선택하며 등록부는 선택 결과를 검증한다.</t>
         </is>
       </c>
       <c r="F16" s="47" t="inlineStr">
         <is>
           <t>적용: 객체 종류는 사건 코드 접두에서 얻고 요청 종류와는 별도 축이다. 객체 종류는 활동·예약 연계·식당·이동·숙소·항공이다.
-인수 REQ-012/AC-01: 동일 객체의 서로 다른 intent를 입력하면 선언된 두 축 계약에 맞는 Team·capability가 선택된다.
-인수 REQ-012/AC-02: 복수 capability Team의 기능 선택 실패·미정 결과를 정상 선택으로 숨기지 않고 인계한다.
+인수 REQ-012/AC-01: 동일 객체에 서로 다른 요청 종류를 입력하면 선언된 두 축 계약에 맞는 담당 팀과 처리 기능이 선택된다.
+인수 REQ-012/AC-02: 여러 처리 기능을 가진 담당 팀이 기능을 선택하지 못하거나 선택 결과를 정하지 못하면 정상 선택으로 처리하지 않고 인계한다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Team은 판정에 필요한 값이 없으면 누락값을 Core에 알리고, Core는 대체 소스로 값을 채워 다시 판정한다. 대체까지 실패하면 치명 결함으로 서버를 중단한다.</t>
+          <t>담당 팀은 판정에 필요한 값이 없으면 누락값을 코어에 알린다. 코어는 대체 소스로 값을 확보해 담당 팀에 다시 판정을 요청한다. 대체까지 실패하면 치명 결함으로 서버를 중단한다.</t>
         </is>
       </c>
       <c r="F21" s="54" t="inlineStr">
@@ -1874,13 +1874,13 @@
       </c>
       <c r="E24" s="47" t="inlineStr">
         <is>
-          <t>핵심 판정 주장마다 출처와 확인 시각을 가진 Evidence를 연결한다.</t>
+          <t>핵심 판정 주장마다 출처와 확인 시각이 기록된 근거 자료를 연결한다.</t>
         </is>
       </c>
       <c r="F24" s="47" t="inlineStr">
         <is>
           <t>적용: API 응답·RAG 규정·고객 신고·합성·Mock·재생 자료.
-인수 REQ-020/AC-01: 핵심 주장별 Evidence의 출처·자료 성격·확인 시각과 적용 대상을 조회할 수 있다.
+인수 REQ-020/AC-01: 핵심 주장별 근거 자료의 출처·자료 성격·확인 시각과 적용 대상을 조회할 수 있다.
 인수 REQ-020/AC-02: 출처 또는 확인 시각이 없는 자료를 확인된 근거로 세지 않고 필수 근거는 대체 소스로 확보한다. 대체까지 실패하면 치명 결함으로 서버를 중단한다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>자료의 제공자 시각·수집 시각·현장 확인 시각·재생 시각을 구별해 표시한다.</t>
+          <t>자료 제공자가 명시한 시각·수집 시각·현장 확인 시각·재생 시각을 구별해 표시한다.</t>
         </is>
       </c>
       <c r="F26" s="54" t="inlineStr">
@@ -2029,7 +2029,7 @@
         <is>
           <t>적용: 시간·예산·잠긴 예약·필수 동행 조건 및 탐색 실패.
 인수 REQ-023/AC-01: 명백한 위반 입력에 위반 대상과 필요한 완화 조건을 반환하고 성공 일정으로 저장하지 않는다.
-인수 REQ-023/AC-02: 해 없음·근거 부족·탐색 상한 도달을 구별한다. 탐색 상한에 도달하면 정해진 범위에서 유효한 안을 찾지 못했다고 설명한다.
+인수 REQ-023/AC-02: 유효한 안이 없는 경우, 필수 근거를 확보하지 못한 경우, 탐색 상한에 도달한 경우를 구별한다. 필수 근거는 대체 소스로 확보하고 대체까지 실패하면 서버를 중단한다. 탐색 상한까지 유효한 안을 찾지 못한 경우에는 정해진 범위에서 찾지 못했다고 설명한다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -2077,7 +2077,7 @@
         <is>
           <t>적용: v11 §6-C-4의 잠정 상한을 인수 설정으로 사용한다. 4단계·단계별 3후보, 완성 조합 3^4=81개, 외부 조회 24회, 120초. (추정) 성능 실측이 아닌 탐색 예산이며 적정 범위는 운영 시험에서 재검증한다.
 인수 REQ-024/AC-01: 설정된 상한과 실제 출발·취소 마감 중 먼저 도래한 한계를 넘기지 않고 실행 내 같은 조회를 캐시한다.
-인수 REQ-024/AC-02: 첫 통과 후보에서 바로 종료하지 않으며 상한에 도달하면 탐색량·탈락 사유를 붙여 인계한다. 버전 충돌 재계산은 최대 1회다.
+인수 REQ-024/AC-02: 첫 통과 후보에서 바로 종료하지 않는다. 상한에 도달하면 통과한 후보 중 하나를 선택하고, 통과한 후보가 없으면 탐색량·탈락 사유를 붙여 인계한다. 버전 충돌 재계산은 최대 1회다.
 검증: 후보 수·외부 호출·경과 시간 계측 및 출발 마감·시간 초과 주입 시험.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -2291,9 +2291,9 @@
       </c>
       <c r="F32" s="63" t="inlineStr">
         <is>
-          <t>적용: 같은 스윕·Trip의 사건과 후속 영향을 함께 처리한다. 선택 규칙은 결정 15에 따라 REQ-049·055의 단일 선택 기준을 적용한다.
-인수 REQ-028/AC-01: 상한 내 통과 후보를 비교할 수 있으면 기준에 맞는 한 안을 고르고 다른 통과 대안은 재요청용으로 최대 2개 보존한다.
-인수 REQ-028/AC-02: 필수값은 대체 소스로 확보하고 대체까지 실패하면 서버를 중단한다. 후보 값이 불확실해도 하나를 고르며 비교 기준이 갈리지 않으면 정규화 후보 ID로 결정하고 선택지를 나열하지 않는다.
+          <t>적용: 같은 감시 회차에서 같은 여행에 발생한 사건과 후속 영향을 함께 처리한다. 선택 규칙은 결정 15에 따라 REQ-049·055의 단일 선택 기준을 적용한다.
+인수 REQ-028/AC-01: 상한 내 통과 후보 중 정해진 기준에 따라 하나를 고른다. 비교 기준으로 우열을 가릴 수 없어도 하나를 선택하고, 다른 통과 대안은 재요청용으로 최대 2개 보존한다.
+인수 REQ-028/AC-02: 필수값은 대체 소스로 확보하고 대체까지 실패하면 서버를 중단한다. 후보 값이 불확실해도 하나를 고르며 비교 기준으로 우열을 가릴 수 없으면 정규화 후보 ID로 결정하고 선택지를 나열하지 않는다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -2444,7 +2444,7 @@
       <c r="F35" s="47" t="inlineStr">
         <is>
           <t>적용: API와 고객 링크의 동일 재요청 경로. 묶음 단위로 처리한다.
-인수 REQ-031/AC-01: 제시했던 대안 선택 또는 되돌림 요청에 현재 잠긴 예약·조건·사건을 적용하고 새 버전과 이력을 남긴다.
+인수 REQ-031/AC-01: 다른 안을 요청하거나 되돌림을 요청하면 현재 잠긴 예약·조건·사건을 적용해 재검증하고 새 버전과 이력을 남긴다.
 인수 REQ-031/AC-02: 현재 휴업한 식당 등 유효하지 않은 과거 내용을 그대로 복원하지 않고 거부·대안·인계 사유를 반환한다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G37" s="47" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H37" s="2" t="n"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G38" s="54" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C·§12</t>
+          <t>근거: 구현계획서 §4-C·§12 · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="G39" s="47" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H39" s="2" t="n"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>자동 실행 시연은 모의 등급 공급자이며 위임 범위 안인 경우에만 승인 대기를 생략한다.</t>
+          <t>자동 실행 시연에서는 공급자 등급이 모의이고 요청이 위임 범위 안인 경우에만 승인 대기를 생략한다.</t>
         </is>
       </c>
       <c r="F40" s="54" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="G40" s="54" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H40" s="2" t="n"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G41" s="47" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H41" s="2" t="n"/>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="G42" s="51" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H42" s="2" t="n"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G43" s="51" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H43" s="2" t="n"/>
@@ -2998,15 +2998,15 @@
       </c>
       <c r="E46" s="51" t="inlineStr">
         <is>
-          <t>API와 고객 링크의 모든 접근은 tenant·Trip 소유 범위를 강제한다.</t>
+          <t>API와 고객 링크의 모든 접근을 테넌트별 여행 소유 범위로 제한한다.</t>
         </is>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
           <t>적용: 품질 범주=보안. 조회·재요청·제안 저장·실행 및 여행별 토큰. 민감정보의 저장·전송·출력 세부 정책은 운영 설계 단계에서 정한다.
-인수 REQ-042/AC-01: 정상 토큰·권한은 소유 여행에만 접근하고 다른 tenant·Trip의 조회·변경·실행을 거부한다.
+인수 REQ-042/AC-01: 유효한 토큰과 권한이 있어도 소유한 여행에만 접근을 허용하고 다른 테넌트 또는 소유 범위 밖 여행의 조회·변경·실행을 거부한다.
 인수 REQ-042/AC-02: 만료·철회·위조 토큰을 거부한다. 토큰 철회가 저장된 이후 시작하는 권한 검사부터 접근을 거부한다. 실행 직전에도 권한을 다시 검사한다.
-검증: 교차 tenant·Trip, 토큰 만료·철회·위조 및 실행 경합 시험.
+검증: 테넌트·여행 간 접근 차단, 토큰 만료·철회·위조 및 실행 경합 시험.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
       </c>
@@ -3112,7 +3112,7 @@
       <c r="F48" s="51" t="inlineStr">
         <is>
           <t>적용: 접점은 개인 에이전트 API와 로그인 없는 토큰 링크다. 직접 일정 편집은 제공하지 않는다. 화면은 운영자 일정·사건·승인·추적 4개와 고객 링크 1개다. 언어는 REQ-057로 분리한다.
-인수 REQ-044/AC-01: 알림을 받지 못해도 링크에서 최신 일정·변경 이유·다른 안·미확정 업체 건·재검토 상태를 확인할 수 있다.
+인수 REQ-044/AC-01: 알림을 받지 못해도 링크에서 최신 일정·변경 이유·미확정 업체 건·재검토 상태를 확인하고 다른 안을 요청할 수 있다.
 인수 REQ-044/AC-02: API와 링크의 재요청이 같은 처리 경로로 연결되고 직접 편집 및 다른 여행 토큰 접근은 거부된다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="E53" s="51" t="inlineStr">
         <is>
-          <t>묶음 후보는 탈락 조건을 먼저 검사한다. 통과한 후보 중 비교 가능한 후보만 정해진 기준 순서대로 비교한다.</t>
+          <t>묶음 후보는 탈락 조건을 먼저 검사한다. 통과한 후보를 정해진 기준 순서대로 비교하고, 우열을 가릴 수 없어도 하나를 선택한다.</t>
         </is>
       </c>
       <c r="F53" s="51" t="inlineStr">
@@ -3421,10 +3421,10 @@
       </c>
       <c r="F54" s="51" t="inlineStr">
         <is>
-          <t>적용: 일정 버전 추가·최신 포인터·Case 전이·outbox 삽입은 같은 트랜잭션이다.
-인수 REQ-050/AC-01: 성공하면 전체 변경과 outbox가 함께 커밋되고 적용 버전당 통지 하나에 원인별 영향·선택 이유·비용·대안·링크를 담는다.
+          <t>적용: 일정 버전 추가, 최신 버전 참조 갱신, 사건 처리 상태 전이, 발송 대기열 기록 추가는 하나의 트랜잭션으로 처리한다.
+인수 REQ-050/AC-01: 성공하면 전체 변경과 발송 대기열 기록을 함께 저장한다. 적용 버전당 통지 하나에 원인별 영향·선택 이유·비용·선택한 안·링크를 담는다.
 인수 REQ-050/AC-02: 중간에 실패하면 해당 작업의 변경 사항을 모두 취소한다. 기존 일정은 유지하되 재검토 상태·영향 항목과 사건·근거·시도·탈락 사유·마감·부분 유효 후보를 별도 인계 기록으로 남긴다. 필수값은 대체 소스로 확보하며 대체까지 실패하면 인계로 대신하지 않고 서버를 중단한다.
-검증: 트랜잭션 각 단계 실패 주입과 일정·포인터·Case·outbox·인계 기록 대조.
+검증: 트랜잭션 각 단계에 실패를 주입하고 일정·최신 버전 참조·사건 처리 상태·발송 대기열·인계 기록을 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
       </c>
@@ -3475,7 +3475,7 @@
         <is>
           <t>적용: 여러 Case·고객 요청·감시 사건이 동일 Trip을 변경하는 경로.
 인수 REQ-051/AC-01: 두 값을 함께 읽고 계산 중 긴 트랜잭션을 유지하지 않는다. 반영 직전 파이썬 선검사와 SQL 조건 모두로 두 값을 검사한다.
-인수 REQ-051/AC-02: 둘 중 하나가 바뀌면 후보를 폐기하고 최신 입력으로 1회 재계산한다. 재충돌하면 인계하며 성공 시 일정·포인터·Case·outbox를 함께 커밋한다.
+인수 REQ-051/AC-02: 둘 중 하나가 바뀌면 후보를 폐기하고 최신 입력으로 1회 재계산한다. 재충돌하면 인계한다. 성공하면 일정·최신 버전 참조·사건 처리 상태·발송 대기열 기록을 하나의 트랜잭션으로 저장한다.
 검증: 동일 Trip의 동시 Case, 사건 개정만 변경, 재충돌 및 커밋 실패 주입 시험.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -3587,7 +3587,7 @@
         <is>
           <t>적용: API=장소·운영·이동·기상, RAG=취소·환급 등 규정, 합성=시험 일정·예약·고객. Mock·재생은 실제 관측과 구별한다.
 인수 REQ-053/AC-01: 자료별 ID·버전·위치·출처·확인일·수량과 확보/일부 확보/확보 예정/확보 불가·중단을 기록하고 용도별 사용 가능/조건부/보류/제외 판정을 별도로 관리한다.
-인수 REQ-053/AC-02: 예정량·공급자 전체량을 내부 확보량에 합산하지 않는다. DDL 파일 존재와 검증·운영 환경 적용을 구별하고 적용 증거가 없으면 적용 여부 미확인으로 기록한다.
+인수 REQ-053/AC-02: 예정량·공급자 전체량을 내부 확보량에 합산하지 않는다. 데이터베이스 구조 정의 파일의 존재 여부와 검증·운영 환경에 실제로 적용했는지를 구별한다. 적용 증거가 없으면 적용 여부 미확인으로 기록한다.
 검증: 문서 검토와 정적 검사로 데이터 목록·원자료 접근·수량·사용 판정·DB 적용 증거를 확인한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -3645,9 +3645,9 @@
       </c>
       <c r="F58" s="51" t="inlineStr">
         <is>
-          <t>적용: 품질 범주=가용성. 마지막 실행·성공 시각, 다음 확인, 오류·지연 대상, 배달 상태. 지원 시간·정상 서비스 정의·집계창·제외 조건·감지 한계·RTO·RPO는 운영 설계 단계에서 정한다.
-인수 REQ-054/AC-01: 감시 중단·지연을 주입하면 설정된 한계 내에 운영 상태에 표시하고 변화 없음으로 처리하지 않는다. 감시 작업만 지연되거나 멈추면 배달 루프는 계속 동작한다. 필수값의 대체 소스까지 실패한 경우에만 치명 결함으로 서버를 중단하며, 이때는 모든 여행의 감시와 알림이 함께 멈춘다.
-인수 REQ-054/AC-02: 일반 배달 예외·타임아웃·연결 오류·작업자 중단을 구별해 상태와 인계 대상을 표시하고 복구 후 일정·감시·outbox의 누락·중복을 검사한다.
+          <t>적용: 품질 범주=가용성. 마지막 실행·성공 시각, 다음 확인, 오류·지연 대상, 배달 상태. 지원 시간·정상 서비스 정의·집계 기간·제외 조건·감지 한계·목표 복구 시간·허용 가능한 데이터 손실 시간 범위는 운영 설계 단계에서 정한다.
+인수 REQ-054/AC-01: 감시 중단·지연을 주입하면 설정된 한계 내에 운영 상태에 표시하고 변화 없음으로 처리하지 않는다. 감시 작업만 지연되거나 멈추면 배달 루프는 계속 동작한다. 필수값의 대체 소스까지 실패하면 치명 결함으로 서버를 중단하며, 이때는 모든 여행의 감시와 알림이 함께 멈춘다.
+인수 REQ-054/AC-02: 일반 배달 예외·시간 초과·연결 오류·배달 작업자 중단을 구별해 상태와 인계 대상을 표시한다. 복구 후 일정·감시·발송 대기열 기록의 누락·중복을 검사한다.
 검증: 장애 주입과 복구 시험. 가용률은 정상 제공 시간/합의한 제공 대상 시간으로 집계한다. MVP 인수는 장애 주입 후 운영 상태 표시와 복구 뒤 누락·중복 0건을 기준으로 판정한다. 가용률 수치 목표는 운영 단계 요구사항으로 별도 관리한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -3760,7 +3760,7 @@
         <is>
           <t>적용: 확정 시나리오 고객 시작 3건: 요식-P3·요식-P7·액-08. 시스템 시작 3건: 액-02·이동-B1·이동-A6. 여섯 사건을 모두 선제 감지로 집계하지 않는다.
 인수 REQ-056/AC-01: 식당 70분 지연과 식당 당일 휴무 고객 신고는 사건 신고로, 활동 재고 질문은 확인 요청으로 잠정 분류해 접수하고 발생원 고객·원문·신고 시각·대상 항목을 기록한다. 공식 대응은 설계 단계에서 확정한다.
-인수 REQ-056/AC-02: 70분 지연은 식당 브레이크타임과 후속 일정을, 당일 휴무는 카드 결제 가능한 대안과 후속 영향을, 재고 질문은 귀가 동선의 다른 지점 하나를 선택해 처리하고 소스가 없는 재고는 판정 입력에서 제외한다.
+인수 REQ-056/AC-02: 70분 지연은 식당의 영업 중 휴식 시간과 후속 일정을 검토해 처리한다. 당일 휴무는 카드 결제 가능한 대안과 후속 영향을 검토해 처리한다. 재고 질문에는 귀가 동선의 다른 지점 하나를 선택해 안내하고, 소스가 없는 재고는 판정 입력에서 제외한다.
 인수 REQ-056/AC-03: 대상 불명은 확인을 요청하고 다른 예약으로 대체하지 않는다. 고객 신고를 공급자 확인으로 바꾸거나 취급 가능 지점을 재고 확보 지점으로 표시하지 않는다.
 검증: (합성) 시나리오 3건의 API·링크 접수, 잠정 분류, 대상 식별, 응답·인계 및 집계 대조.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
@@ -4033,14 +4033,14 @@
       </c>
       <c r="E65" s="57" t="inlineStr">
         <is>
-          <t>소스 또는 Team을 추가해도 기존 계약·권한·필수값 대체 조회와 대체 실패 시 서버 중단·일정 정합성을 유지한다.</t>
+          <t>소스 또는 담당 팀을 추가해도 기존 계약·권한·일정 정합성을 유지한다. 필수값의 대체 조회와 대체 실패 시 서버 중단 규칙도 유지한다.</t>
         </is>
       </c>
       <c r="F65" s="57" t="inlineStr">
         <is>
           <t>적용: 품질 범주=확장. 기능·연동 추가를 우선 검수하고 용량 확장의 기준·목표 규모·허용 자원·비용·증설 시간은 운영·원가 검토 단계에서 정한다. 도시 확장은 결정 12의 테스트 검증 이후 별도 범위다.
 인수 REQ-061/AC-01: (Mock) 소스 또는 Team 하나를 추가해 등록·도달성·capability·출처·권한·필수값 대체 조회와 대체 실패 시 서버 중단이 기존 계약과 함께 동작하고 기존 AC 회귀에서 중대 정합성·권한 위반이 발생하지 않는다.
-인수 REQ-061/AC-02: 미등록 capability·호환되지 않는 스키마·권한 우회 입력을 거부한다. 용량 목표가 미확정이면 확장 성능 완료 또는 다른 도시 지원 완료로 표시하지 않는다.
+인수 REQ-061/AC-02: 미등록 처리 기능·호환되지 않는 데이터 구조·권한 우회 입력을 거부한다. 용량 목표가 미확정이면 확장 성능 완료 또는 다른 도시 지원 완료로 표시하지 않는다.
 검증: (Mock) 확장 등록·오류 주입과 기존 계약 회귀 검사. 용량 확장은 별도 합의한 부하 시험.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>
@@ -4093,7 +4093,7 @@
 인수 REQ-062/AC-02: 기동 때 필수 소스의 설정·구현을 검사하고 소스 누락·미구현이면 서버가 기동하지 않는다.
 인수 REQ-062/AC-03: 1차 소스 실패 시 선언된 대체 소스로 값을 구하고 출처와 확인 시각을 보존한다. 모델이 값을 지어내거나 모름으로 반환하지 않는다.
 인수 REQ-062/AC-04: 운영 중 대체 소스까지 실패하면 치명 결함으로 서버를 중단하며 다른 모든 여행의 감시·알림도 함께 멈춘다.
-인수 REQ-062/AC-05: 후보 값이 불확실해도 하나를 고르고 선택지를 나열하지 않는다. 비교 기준이 갈리지 않으면 정규화 후보 ID로 결정하고 적용 전 전체 재검증을 수행한다.
+인수 REQ-062/AC-05: 후보 값이 불확실해도 하나를 고르고 선택지를 나열하지 않는다. 비교 기준으로 우열을 가릴 수 없으면 정규화 후보 ID로 결정하고 적용 전 전체 재검증을 수행한다.
 검증: (Mock) 필수값별 대체 소스 선언 검사, 설정 누락·미구현 시 기동 거부, 1차 실패 시 대체 성공, 대체 실패 시 서버 중단과 전체 감시·알림 중단, 불확실·동률 후보 단일 선택 시험.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
         </is>

--- a/program/산출물양식/w2/제출본/[기획] 요구사항 정의서_2차_여행.xlsx
+++ b/program/산출물양식/w2/제출본/[기획] 요구사항 정의서_2차_여행.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G37" s="47" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16: DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H37" s="2" t="n"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G38" s="54" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C·§12 · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
+          <t>근거: 구현계획서 §4-C·§12 · MVP 다음(결정 16: DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="G39" s="47" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16: DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H39" s="2" t="n"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="G40" s="54" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16: DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H40" s="2" t="n"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G41" s="47" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16: DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H41" s="2" t="n"/>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="G42" s="51" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16: DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H42" s="2" t="n"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G43" s="51" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16 — DoD-14~21 은 MVP 판정 제외)</t>
+          <t>근거: 구현계획서 §4-C · MVP 다음(결정 16: DoD-14~21 은 MVP 판정 제외)</t>
         </is>
       </c>
       <c r="H43" s="2" t="n"/>
@@ -3112,7 +3112,7 @@
       <c r="F48" s="51" t="inlineStr">
         <is>
           <t>적용: 접점은 개인 에이전트 API와 로그인 없는 토큰 링크다. 직접 일정 편집은 제공하지 않는다. 화면은 운영자 일정·사건·승인·추적 4개와 고객 링크 1개다. 언어는 REQ-057로 분리한다.
-인수 REQ-044/AC-01: 알림을 받지 못해도 링크에서 최신 일정·변경 이유·미확정 업체 건·재검토 상태를 확인하고 다른 안을 요청할 수 있다.
+인수 REQ-044/AC-01: 알림을 받지 못해도 링크에서 최신 일정·변경 이유·다른 안·미확정 업체 건·재검토 상태를 확인하고 다른 안을 요청할 수 있다.
 인수 REQ-044/AC-02: API와 링크의 재요청이 같은 처리 경로로 연결되고 직접 편집 및 다른 여행 토큰 접근은 거부된다.
 검증: 자동 시험으로 정상 입력과 위반·실패 입력의 응답·저장 상태를 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
@@ -3422,7 +3422,7 @@
       <c r="F54" s="51" t="inlineStr">
         <is>
           <t>적용: 일정 버전 추가, 최신 버전 참조 갱신, 사건 처리 상태 전이, 발송 대기열 기록 추가는 하나의 트랜잭션으로 처리한다.
-인수 REQ-050/AC-01: 성공하면 전체 변경과 발송 대기열 기록을 함께 저장한다. 적용 버전당 통지 하나에 원인별 영향·선택 이유·비용·선택한 안·링크를 담는다.
+인수 REQ-050/AC-01: 성공하면 전체 변경과 발송 대기열 기록을 함께 저장한다. 적용 버전당 통지 하나에 원인별 영향·선택 이유·비용·대안·링크를 담는다.
 인수 REQ-050/AC-02: 중간에 실패하면 해당 작업의 변경 사항을 모두 취소한다. 기존 일정은 유지하되 재검토 상태·영향 항목과 사건·근거·시도·탈락 사유·마감·부분 유효 후보를 별도 인계 기록으로 남긴다. 필수값은 대체 소스로 확보하며 대체까지 실패하면 인계로 대신하지 않고 서버를 중단한다.
 검증: 트랜잭션 각 단계에 실패를 주입하고 일정·최신 버전 참조·사건 처리 상태·발송 대기열·인계 기록을 대조한다.
 시험 조건: 본문 사례의 (합성) 입력·(Mock) 응답은 시험 계획이며 실측 자료가 아니다. 실제 실행 시 빌드·설정·데이터 버전·환경·표본·실행 ID를 기록한다.</t>
